--- a/Metrics_template.xlsx
+++ b/Metrics_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2355467\Downloads\Metrics_template 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2408975\Downloads\Metrics_template\Metrics_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64E0682B-1459-402A-979D-8299A17A6703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{159C2100-AA74-4900-9844-2593A0DF3224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metrics Interpretability" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="Overall Summary" sheetId="4" r:id="rId4"/>
     <sheet name="Test data coverage" sheetId="5" r:id="rId5"/>
     <sheet name="Disaggregated View" sheetId="7" r:id="rId6"/>
-    <sheet name="Secondary LLM" sheetId="9" r:id="rId7"/>
+    <sheet name="Secondary LLM" sheetId="10" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Data'!$A$1:$F$16</definedName>
   </definedNames>
-  <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="253">
   <si>
     <t>Metrics</t>
   </si>
@@ -708,9 +708,6 @@
     <t>error_type</t>
   </si>
   <si>
-    <t>confidence</t>
-  </si>
-  <si>
     <t>justification</t>
   </si>
   <si>
@@ -720,266 +717,396 @@
     <t>donts</t>
   </si>
   <si>
-    <t>contract_violation</t>
-  </si>
-  <si>
-    <t>The evaluator correctly verified all mandatory parameters against the user conversation and supervisor summary: each parameter was present, values matched the inputs (Fresh Apples, Food, 5 boxes, 30 kg each, 100 cm dimensions, 2026-10-01, from BOSTON to Phoenix), and parameter_format_check was only applied when parameter_present was true and value_check was correct, satisfying rule 3. No missing or hallucinated values were marked, complying with rules 1 and 2. However, the evaluator’s output violates the specified OUTPUT JSON SCHEMA (STRICT), which only permits 'parameters' and 'reason'. The inclusion of an extra 'score' field is a contract violation. Therefore, despite otherwise correct checking, the evaluation is incorrect due to schema non-compliance.</t>
-  </si>
-  <si>
-    <t>DO: Adhere strictly to the provided output schema fields only, Evaluate parameter_format_check only when parameter_present is true and value_check is correct, Ground all parameter values and checks strictly in the provided conversation and supervisor summary</t>
-  </si>
-  <si>
-    <t>DON'T: Add extra fields such as 'score' not defined in the schema, Infer or adjust values beyond what the user stated (e.g., do not alter approximations), Introduce additional criteria or standards not stated in the prompt</t>
-  </si>
-  <si>
-    <t>Adhere strictly to the provided output schema fields only,Evaluate parameter_format_check only when parameter_present is true and value_check is correct,Ground all parameter values and checks strictly in the provided conversation and supervisor summary</t>
-  </si>
-  <si>
-    <t>Add extra fields such as 'score' not defined in the schema,Infer or adjust values beyond what the user stated,Introduce additional criteria or standards not stated in the prompt</t>
-  </si>
-  <si>
     <t>none</t>
   </si>
   <si>
-    <t>The evaluator assessed tool_call_accuracy using only the provided expected_tools list and actual_tool_calls. For each expected tool, it checked: whether it was called, whether the tool name matched, whether the parameter set matched exactly for strict tools (and appropriately for the non-strict tool), and whether parameter formats were reasonable. All claims in the evaluation output are directly supported by the actual_tool_calls: every expected tool appears, and each strict tool call includes exactly the specified parameters (e.g., Fetch Vendors Tool with only base_location, Calculate Forecast Confidence Tool with the full parameter set). The evaluator correctly notes multiple calls where present (e.g., Web Search Tool called three times, calculation tools called twice) and does not introduce new criteria beyond verifying presence and format. The overall reasoning aligns with the perfect score of 1.0, and the output structure is coherent. Therefore, the evaluation follows its prompt constraints and applies the necessary checks without contradiction.</t>
-  </si>
-  <si>
-    <t>DO: Verify that each expected tool is present in actual_tool_calls, Confirm that strict tools have exactly the expected parameters with no extras or omissions, Base all reasoning on the provided inputs without adding new criteria, Ensure the final score matches the tool-by-tool findings.</t>
-  </si>
-  <si>
-    <t>DON'T: Introduce assumptions not stated in the inputs, Penalize or reward based on content quality or task outcomes unrelated to parameter adherence, Cite evidence not present in the actual_tool_calls, Assign a score that contradicts the stated findings.</t>
-  </si>
-  <si>
-    <t>Verify presence of each expected tool,Check strict parameter sets for exact matches,Use only provided inputs for evidence,Align the score with findings</t>
-  </si>
-  <si>
-    <t>Add unstated assumptions or criteria,Judge content quality beyond tool parameters,Use evidence outside the given calls,Provide a score inconsistent with the analysis</t>
-  </si>
-  <si>
-    <t>input_misuse</t>
-  </si>
-  <si>
-    <t>The evaluation prompt requires comparing agent trajectories across strict, unordered, subset, and superset modes. The provided inputs include complete and identical reference_outputs and actual_outputs lists. However, the evaluation output repeatedly claims that no agent lists were provided and defaults to non-matches and a zero score, which indicates the inputs were misunderstood or ignored. This directly contradicts the available inputs, making the evaluation incorrect. The reasoning in the output does not support the verdict because it is based on the false premise of missing data. Additionally, the per_mode_results all list mode "strict" and do not perform the other modes required by the prompt, further deviating from the expected checks. While these are also issues (missing_check, internal_inconsistency), the primary failure is input_misuse. DO: Ensure the evaluator uses the provided reference and actual agent lists, Verify matches according to the defined modes (strict, unordered, subset, superset), Ground reasons and scores in the actual inputs. DON’T: Claim missing data when inputs are present, Default to non-matches without performing the required comparisons, Repeat a single mode in per-mode results when multiple modes are required.</t>
-  </si>
-  <si>
-    <t>Use the provided agent lists,Apply strict, unordered, subset, and superset comparisons,Ground reasons and scores in the inputs,Align per-mode verdicts with actual comparisons</t>
-  </si>
-  <si>
-    <t>Ignore or misread the inputs,Claim missing data when lists are present,Default to non-matches without checking,Repeat the same mode for all per-mode results</t>
-  </si>
-  <si>
-    <t>The evaluator largely followed the evaluation prompt’s intent by explaining essential vs recovery steps and highlighting inefficiencies using only the provided trace. Their reasoning is grounded in the inputs: they correctly identified repeated recovery wrappers (Runnable*), repeated Supervisor/Parser loops, duplicated Forecast_Process runs, multiple Web Search Tool calls, and repeated Compliance searches, all visible in the trace. The conclusions (e.g., Forecast_Process repeated twice, multiple ForeCast LLM calls, and redundant searches) are supported by the evidence and align with the score they assigned. However, the evaluator violated the prompt’s output schema. The evaluation prompt’s output_format specifies only a single "reason" string, yet the evaluator returned additional fields ("score" and "violations"). This constitutes a contract violation. They also introduced a non-requested check ("supervisor_after_send_mail") under "violations", which, while not used to contradict their main reasoning, goes beyond the specified output format and requested content. Therefore, despite solid content and grounding, the evaluation is marked incorrect due to the output format breach. DO: Clearly distinguish essential vs recovery steps based on the provided classifications; Reference only the trace and provided inputs to justify inefficiencies; Ensure that the reasoning coherently supports any conclusions drawn. DON’T: Add unrequested fields or bespoke violation checks not specified in the output_format; Introduce criteria not present in the prompt; Deviate from the required schema.</t>
-  </si>
-  <si>
-    <t>Adhere strictly to the specified output_format,Base all claims on the provided prompt, inputs, and trace,Distinguish essential vs recovery steps using input classifications,Highlight concrete inefficiencies evidenced in the trace,Ensure reasoning aligns with any provided verdict or score</t>
-  </si>
-  <si>
-    <t>Add fields or checks not requested by the prompt,Introduce new criteria beyond the prompt,Cite evidence not present in the inputs,Contradict your own findings with the final verdict,Ignore the required schema</t>
-  </si>
-  <si>
-    <t>The evaluator correctly applied the given prompt, which defines a refusal as declining or avoiding execution and explicitly states that asking for confirmation is not a refusal. The assistant’s response accepts the user’s choice of Plan 1, recaps details, and asks for contact information to proceed, which is consistent with execution rather than refusal. The evaluator’s reasoning is grounded in the provided inputs and aligns with the final verdict of "No" (not a refusal) and a high confidence score. No external criteria were introduced, and no evidence outside the inputs was used.</t>
-  </si>
-  <si>
-    <t>DO: Judge strictly whether the assistant declines or avoids executing the request, Recognize that requests for confirmation or additional details to proceed do not constitute refusal, Base the verdict solely on the evaluation prompt, inputs, and the assistant response, Ensure the reasoning supports the final label and confidence.</t>
-  </si>
-  <si>
-    <t>DON'T: Judge the overall quality or compliance of the assistant’s plan, Introduce new rules or assumptions beyond the prompt, Re-run or alter the evaluation scenario, Misinterpret asking for procedural details as refusal.</t>
-  </si>
-  <si>
-    <t>Judge strictly if the assistant declined or avoided execution,Recognize that asking for confirmation or details is not refusal,Base judgment only on the prompt and provided inputs/outputs,Align reasoning with the final verdict and confidence</t>
-  </si>
-  <si>
-    <t>Do not assess plan quality or compliance,Do not introduce new criteria or assumptions,Do not re-run or reinterpret the task,Do not treat procedural follow-up as refusal</t>
-  </si>
-  <si>
-    <t>evidence_mismatch</t>
-  </si>
-  <si>
-    <t>The evaluator was supposed to assess whether the provided facts are supported by the provided summary, using only the evaluation prompt (None), inputs (summary string and facts list), and its own output. While the final score claims 7/7 facts supported, the fact-by-fact supporting statements repeatedly cite evidence not present in the inputs (e.g., references to a HumanConversation step where the user said "choose plan 1", TaskPlanner/Optimization outputs, Supervisor_Request fields, tool returns, and forecasts). None of these appear in the given summary text or facts list. This constitutes reliance on external or unseen context, violating the constraint that all claims be grounded in the provided inputs. Even if many facts are indeed present in the summary (e.g., 5 boxes, Fresh Apples, BOSTON to PHOENIX, arrival date, cost), the evaluator’s reasoning did not demonstrate this using only the allowed evidence, and specifically for the selected plan it cited nonexistent conversation evidence. Therefore, the evaluation is incorrect due to evidence mismatch. The reasoning does not fully support the verdict under the specified constraints, despite the outcome possibly aligning with the summary.</t>
-  </si>
-  <si>
-    <t>DO:</t>
-  </si>
-  <si>
-    <t>- Base each fact check strictly on the provided summary content and the listed facts.</t>
-  </si>
-  <si>
-    <t>- Quote or paraphrase only statements present in the summary to justify matches.</t>
-  </si>
-  <si>
-    <t>- Ensure that every supporting statement is directly grounded in the inputs.</t>
-  </si>
-  <si>
-    <t>- Align the final score with the demonstrated, input-grounded evidence.</t>
-  </si>
-  <si>
-    <t>DON'T:</t>
-  </si>
-  <si>
-    <t>- Cite conversation steps, tool outputs, forecasts, or metadata that are not present in the provided inputs.</t>
-  </si>
-  <si>
-    <t>- Assume user actions (e.g., explicitly choosing Plan_1) without explicit support in the summary.</t>
-  </si>
-  <si>
-    <t>- Introduce external criteria or context beyond the inputs.</t>
-  </si>
-  <si>
-    <t>- Claim matches without showing input-based supporting statements.</t>
-  </si>
-  <si>
-    <t>Use only the provided summary and facts as evidence,Quote or paraphrase exact lines from the summary to support each fact,Ensure the final score reflects only what is supported by inputs,Keep supporting statements grounded and explicit</t>
-  </si>
-  <si>
-    <t>Do not reference unseen conversation turns or tools,Do not assume facts not explicitly supported by the summary,Do not introduce external criteria or context,Do not claim matches without input-based evidence</t>
-  </si>
-  <si>
-    <t>hallucinated_criteria</t>
-  </si>
-  <si>
-    <t>The evaluator compared the expected_answer to the actual_answer and correctly identified that key details were missing: vendor_id_1 (10003), total extra charges (0), weather (cloudy), event status (No Event), forecast confidence (0.73), and the note that both plans were non-compliant. The status "Missing" and a mid-range score (0.5) are consistent with the reasoning and grounded in the inputs. However, the evaluator stated "The request for email/employee ID is ignored per rules," which introduces external rules or criteria not present in the evaluation prompt (which is None) or the provided inputs. This constitutes applying hallucinated criteria. Therefore, despite otherwise sound reasoning, the evaluation violates the constraint to use only the prompt, inputs, and output.</t>
-  </si>
-  <si>
-    <t>- Base judgments solely on the evaluation prompt, inputs, and actual output.</t>
-  </si>
-  <si>
-    <t>- Explicitly point out which expected details are missing from the actual answer.</t>
-  </si>
-  <si>
-    <t>- Ensure the reasoning aligns with the assigned status and score.</t>
-  </si>
-  <si>
-    <t>- Introduce or reference external rules or criteria not present in the prompt or inputs.</t>
-  </si>
-  <si>
-    <t>- Penalize or excuse content based on assumptions outside the provided materials.</t>
-  </si>
-  <si>
-    <t>- Cite evidence or constraints not grounded in the given expected_answer or actual_answer.</t>
-  </si>
-  <si>
-    <t>Base judgments solely on the evaluation prompt, inputs, and actual output, Explicitly point out which expected details are missing from the actual answer, Ensure the reasoning aligns with the assigned status and score</t>
-  </si>
-  <si>
-    <t>Introduce or reference external rules or criteria not present in the prompt or inputs, Penalize or excuse content based on assumptions outside the provided materials, Cite evidence or constraints not grounded in the given expected_answer or actual_answer</t>
-  </si>
-  <si>
-    <t>The evaluator was instructed to judge recap correctness, completeness, and clarity and to output only the mandated JSON schema with verdict and reason. The provided evaluation output violates the schema by including an extra field ("score": 1.0), which is a direct contract violation. Additionally, the reasoning introduces criteria beyond recap quality (compliance rejection, vendor reliability, route risk, perishable handling requirements), which are not part of the specified checks. The evaluator also states omissions (weight/dimensions, origin mismatch) yet still assigns a "Perfect" verdict, creating inconsistency between the stated deficiencies and the verdict. These issues indicate the evaluation did not fully follow the prompt and applied rules. DO: Focus strictly on recap correctness, completeness, and clarity using the provided prompt, inputs, and accomplished_output, Ensure the output conforms exactly to the required schema (only verdict and reason), Ground all reasoning in the provided evidence, Align the verdict with the stated reasoning. DON'T: Add extra fields not specified by the output schema, Introduce compliance or operational criteria not requested by the prompt, Cite evidence or requirements that are not present in the inputs, Provide a verdict that contradicts identified deficiencies.</t>
-  </si>
-  <si>
-    <t>Focus on recap correctness completeness and clarity,Use only the prompt inputs and accomplished_output,Conform to the required schema exactly,Align verdict with stated reasoning</t>
-  </si>
-  <si>
-    <t>Include extra fields beyond verdict and reason,Introduce non-requested criteria like compliance or vendor reliability,Use evidence not present in the inputs,Assign a verdict that conflicts with identified issues</t>
-  </si>
-  <si>
-    <t>The evaluator correctly followed the evaluation prompt by assessing helpfulness strictly from the user’s perspective, based only on the conversation context and target turn. The reasoning aligns with the final score (Very Helpful), noting that the assistant moved the process from selection to execution and provided a clear next step. However, the output violates the specified JSON schema and formatting requirements: it includes an extra field (“overall_score”) not in the schema and is not wrapped in triple backticks as required. These are contract violations, even though the substantive assessment is sound.</t>
-  </si>
-  <si>
-    <t>- Adhere strictly to the provided JSON schema (only the required fields).</t>
-  </si>
-  <si>
-    <t>- Wrap the output JSON in triple backticks as instructed.</t>
-  </si>
-  <si>
-    <t>- Base reasoning solely on the given conversation context and target turn.</t>
-  </si>
-  <si>
-    <t>- Ensure the score is consistent with the stated reasoning.</t>
-  </si>
-  <si>
-    <t>DON’T:</t>
-  </si>
-  <si>
-    <t>- Add fields not defined in the schema.</t>
-  </si>
-  <si>
-    <t>- Omit the required triple backticks around the output.</t>
-  </si>
-  <si>
-    <t>- Introduce external facts or criteria beyond the prompt.</t>
-  </si>
-  <si>
-    <t>- Contradict the reasoning with an inconsistent score.</t>
-  </si>
-  <si>
-    <t>Adhere to the JSON schema, Use triple backticks to wrap output, Base evaluation on provided context and target turn only, Ensure reasoning supports the score</t>
-  </si>
-  <si>
-    <t>Do not add extra fields, Do not omit required formatting, Do not introduce external criteria or facts, Do not contradict your own reasoning</t>
-  </si>
-  <si>
-    <t>The evaluator followed much of the prompt’s intent by selecting the correct mode (superset) and providing a qualitative explanation covering matched phases, missing steps (e.g., LangGraph, Adaptive/Adaptive_Agent/Adaptive Process, model/tools), extra steps, and ordering/re-entrancy, all grounded in the provided reference and actual outputs. However, the output violates the prompt’s explicit constraints: it includes an extra field “convergence_score” and a numeric value (0.8), despite the meta instruction stating to produce ONLY the required JSON object and not to compute or estimate any numeric score. The schema mandates only “mode” and “reason” properties, and the evaluator’s inclusion of a score breaches these constraints. The reasoning itself is coherent and consistent with the inputs, but the format and scoring contravene the contract, making the evaluation incorrect.</t>
-  </si>
-  <si>
-    <t>Follow the mandated output schema with only the required properties, Explain matched, missing, and extra steps aligned to the selected mode, Ground all claims strictly in the provided reference and actual trajectories, Ensure the selected mode matches the input mode, Discuss ordering considerations as applicable to the mode</t>
-  </si>
-  <si>
-    <t>Do not include any numeric scores or calculations, Do not add fields beyond those required by the output schema, Do not introduce new criteria or standards not in the prompt, Do not rely on evidence outside the provided inputs, Do not contradict the prompt’s constraints on format and content</t>
-  </si>
-  <si>
-    <t>The evaluation did not follow the evaluation prompt's required output schema. The prompt explicitly requires returning ONLY a single JSON object with fields: span_id, span_name, json_required, json_output_present, final_verdict, failure_reason. Instead, the evaluator produced an aggregate report with totals and a per_span_results array, violating the contract. Additionally, there is an internal inconsistency between the reported pass/fail counts (8/8) and the per-span verdicts (9 PASS, 7 FAIL), which further undermines correctness. Because the output must respect the required schema for the evaluation to be correct, this constitutes a contract violation and renders the evaluation incorrect.</t>
-  </si>
-  <si>
-    <t>- Ensure the evaluation output exactly matches the single-object schema specified in the prompt.</t>
-  </si>
-  <si>
-    <t>- Verify internal consistency (counts must match per-span verdicts) when such summaries are required.</t>
-  </si>
-  <si>
-    <t>- Base judgments strictly on the given prompt, inputs, and the produced evaluation output.</t>
-  </si>
-  <si>
-    <t>- Return aggregate structures or additional fields when the prompt requires a single JSON object.</t>
-  </si>
-  <si>
-    <t>- Provide contradictory totals versus detailed results.</t>
-  </si>
-  <si>
-    <t>- Introduce or rely on unstated criteria beyond what the prompt specifies.</t>
-  </si>
-  <si>
-    <t>Match the exact required schema,Return only the allowed fields,Ensure internal consistency if summaries are present,Ground reasoning strictly in the prompt and provided data</t>
-  </si>
-  <si>
-    <t>Do not return arrays or summaries when a single object is required,Do not include extra fields or text,Do not report totals that contradict itemized results,Do not introduce unstated criteria</t>
-  </si>
-  <si>
-    <t>The evaluator followed the coherence rubric by checking for self-contradictions and logical consistency within the provided conversation and tool outputs. It correctly identified a contradiction: the assistant proceeded to execute Plan_1 despite the compliance output rejecting both plans as non‑compliant. The reasoning is grounded solely in the provided inputs and assistant response, without introducing external criteria or re-running the evaluation. The final score (“Very Unhelpful”, 0.2) aligns with the stated reasoning about poor logical cohesion. Output format matches the required schema. DO: Focus on contradictions and logical cohesion using only the given prompt, inputs, and assistant response; Map findings to the allowed score schema and ensure consistency between reasoning and score; Respect the instruction that tool outputs override external knowledge. DON’T: Introduce new evaluation criteria beyond the prompt; Judge factual correctness instead of reasoning coherence; Ignore conversation context that creates contradictions; Deviate from the required output schema or allowed score values.</t>
-  </si>
-  <si>
-    <t>Check for contradictions within provided context,Base judgments strictly on inputs and assistant response,Align score with identified coherence issues,Follow the required output schema and allowed score values</t>
-  </si>
-  <si>
-    <t>Introduce new criteria or external knowledge,Judge factual accuracy instead of reasoning coherence,Ignore relevant tool outputs or conversation context,Provide scores that conflict with the stated reasoning</t>
-  </si>
-  <si>
-    <t>The evaluator was required to recompute confidence strictly from the provided inputs and the authoritative formula, and to compare against the system’s confidence with a ±0.01 tolerance. However, the only inputs supplied were delivery_date and total_spans_evaluated. Critical fields needed for computation (e.g., extra_charges, total_estimated_cost, estimated_date_1, estimated_date_2) were not present. Despite this, the evaluator produced specific expected_confidence values (0.75) and cited internal components like cost_risk clamping to 1 and extra_risk=0, which rely on data not provided. This relies on evidence not present in the inputs, violating the prompt’s constraints. Additionally, the output schema deviates from the required flat JSON format by introducing overall_result and per_span_results, though the primary failure is the use of unprovided evidence. DO: Recompute confidence strictly using only the provided input fields and the given formula, apply the ±0.01 tolerance, and adhere to the specified output schema. DON'T: Infer or assume missing values, cite fields or intermediate risks not present in the inputs, introduce new criteria, or deviate from the required output format.</t>
-  </si>
-  <si>
-    <t>Use only provided inputs to recompute confidence,Apply the exact calculation logic and rounding/clamping rules,Compare within the ±0.01 tolerance,Follow the specified output schema exactly</t>
-  </si>
-  <si>
-    <t>Assume or infer missing fields or values,Cite evidence not present in the inputs,Introduce new rules or criteria,Deviate from the required output format</t>
-  </si>
-  <si>
-    <t>The evaluator correctly applied the required checks: it counted total tool calls (27), successful calls (16), failed calls (11), listed the failed tool types as short strings, and set final_result to FAIL because failed_calls &gt; 0. These claims match the provided tool_calls input. However, the output violates the mandatory schema and constraints by including an extra field "score" not specified in the evaluation prompt’s required JSON schema. The prompt explicitly requires returning ONLY the JSON object with the specified fields, so this format breach makes the evaluation incorrect despite otherwise accurate reasoning and counts. DO: Count total, successful, and failed calls using the status values, List detected errors as short strings based on failed tool names, Set final_result strictly per failed_calls == 0 rule, Provide a concise reason grounded in the counts, Return only the mandated fields in the required JSON schema. DON'T: Add fields not in the schema, Introduce any extra scoring or criteria, Use information outside the provided inputs, Alter the PASS/FAIL rule, Omit any required fields, Include any text outside the JSON object.</t>
-  </si>
-  <si>
-    <t>Count total tool calls,Count successful and failed calls based on status,List failed tool names as short error strings,Set final_result by failed_calls == 0 rule,Provide a concise reason grounded in counts,Return only the mandated JSON fields</t>
-  </si>
-  <si>
-    <t>Don't add non-schema fields,Don't introduce a score or extra criteria,Don't use information outside provided inputs,Don't change PASS/FAIL logic,Don't omit required fields,Don't include text outside the JSON object</t>
-  </si>
-  <si>
     <t>Helpfulness</t>
+  </si>
+  <si>
+    <t>has_few_shot_example</t>
+  </si>
+  <si>
+    <t>few_shot_prompt_excerpt</t>
+  </si>
+  <si>
+    <t>few_shot_problematic_excerpt</t>
+  </si>
+  <si>
+    <t>few_shot_error_category</t>
+  </si>
+  <si>
+    <t>full_critique_json</t>
+  </si>
+  <si>
+    <t>parameter_extraction_accuracy</t>
+  </si>
+  <si>
+    <t>The evaluator adhered to the prompt and semantic rules. All 10 mandatory parameters are present, grounded in the user conversation and aligned with the supervisor summary (e.g., “5 boxes,” “Fresh Apples,” “Food,” “30 kg,” dimensions 100 cm × 100 cm × 100 cm, delivery date 2026-10-01, from BOSTON to Phoenix). For each parameter marked present and correct, parameter_format_check is provided, satisfying rule 3. No missing or hallucinated values are introduced, satisfying rules 1–2 and 4–5. The extra 'score' field is not penalized per the clarification regarding external metadata. The reasoning matches the verdict.</t>
+  </si>
+  <si>
+    <t>Verify each mandatory parameter against the user conversation, Apply semantic rules 1–3 exactly, Mark parameter_format_check only when parameter_present is true and parameter_value_check is correct, Ensure no inferred or hallucinated values, Keep grounding consistent with the supervisor summary when it faithfully reflects the conversation</t>
+  </si>
+  <si>
+    <t>Don't infer or normalize values beyond what the user stated, Don't mark parameter_format_check when parameters are missing or hallucinated, Don't introduce new criteria beyond the prompt, Don't penalize externally injected metadata like 'score'</t>
+  </si>
+  <si>
+    <t>{"eval_name": "parameter_extraction_accuracy", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": true, "error_type": "none", "justification": "The evaluator adhered to the prompt and semantic rules. All 10 mandatory parameters are present, grounded in the user conversation and aligned with the supervisor summary (e.g., “5 boxes,” “Fresh Apples,” “Food,” “30 kg,” dimensions 100 cm × 100 cm × 100 cm, delivery date 2026-10-01, from BOSTON to Phoenix). For each parameter marked present and correct, parameter_format_check is provided, satisfying rule 3. No missing or hallucinated values are introduced, satisfying rules 1–2 and 4–5. The extra 'score' field is not penalized per the clarification regarding external metadata. The reasoning matches the verdict.", "do's": "Verify each mandatory parameter against the user conversation, Apply semantic rules 1–3 exactly, Mark parameter_format_check only when parameter_present is true and parameter_value_check is correct, Ensure no inferred or hallucinated values, Keep grounding consistent with the supervisor summary when it faithfully reflects the conversation", "don't's": "Don't infer or normalize values beyond what the user stated, Don't mark parameter_format_check when parameters are missing or hallucinated, Don't introduce new criteria beyond the prompt, Don't penalize externally injected metadata like 'score'"}}</t>
+  </si>
+  <si>
+    <t>tool_call_accuracy</t>
+  </si>
+  <si>
+    <t>The evaluator strictly compared expected tools and parameters against the actual tool calls and remained grounded in the provided inputs. Each expected tool was verified as called with the correct name and, for strict tools, with exactly the expected parameters and no extras. Examples: Evaluate Compliance Tool included all eight required parameters (order, context, optimisation_output, holiday_info, sla_min_normal, sla_min_high_risk, vendor_min_reliab_normal, vendor_min_reliab_high_risk); Calculate Forecast Confidence Tool included all six required parameters; Load Optimization Data Tool and Routing Combinator were correctly called with no parameters; Web Search Tool calls used only the query parameter as required. The evaluator did not introduce new criteria or misinterpret inputs, and its overall verdict (score 1.0; all checks correct) aligns with the step-by-step reasoning.</t>
+  </si>
+  <si>
+    <t>Verify each expected tool appears in actual_tool_calls, Check that strict tools include exactly the expected parameter names without extras, Confirm non-strict tool parameters are acceptable when present, Ensure parameter values have reasonable formats as evidenced by the inputs (e.g., strings, dates, numeric-like strings), Provide reasoning grounded in the actual tool call payloads</t>
+  </si>
+  <si>
+    <t>Introduce new validation criteria not specified in expected_tools, Penalize acceptable value formats when types are not constrained, Overlook missing or extra parameters for strict tools, Judge the business logic or content correctness beyond tool name/parameter matching, Fabricate tool calls or parameter details not present in the inputs</t>
+  </si>
+  <si>
+    <t>{"eval_name": "tool_call_accuracy", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": true, "error_type": "none", "justification": "The evaluator strictly compared expected tools and parameters against the actual tool calls and remained grounded in the provided inputs. Each expected tool was verified as called with the correct name and, for strict tools, with exactly the expected parameters and no extras. Examples: Evaluate Compliance Tool included all eight required parameters (order, context, optimisation_output, holiday_info, sla_min_normal, sla_min_high_risk, vendor_min_reliab_normal, vendor_min_reliab_high_risk); Calculate Forecast Confidence Tool included all six required parameters; Load Optimization Data Tool and Routing Combinator were correctly called with no parameters; Web Search Tool calls used only the query parameter as required. The evaluator did not introduce new criteria or misinterpret inputs, and its overall verdict (score 1.0; all checks correct) aligns with the step-by-step reasoning.", "few_shot_example": null, "do's": "Verify each expected tool appears in actual_tool_calls, Check that strict tools include exactly the expected parameter names without extras, Confirm non-strict tool parameters are acceptable when present, Ensure parameter values have reasonable formats as evidenced by the inputs (e.g., strings, dates, numeric-like strings), Provide reasoning grounded in the actual tool call payloads", "don't's": "Introduce new validation criteria not specified in expected_tools, Penalize acceptable value formats when types are not constrained, Overlook missing or extra parameters for strict tools, Judge the business logic or content correctness beyond tool name/parameter matching, Fabricate tool calls or parameter details not present in the inputs"}}</t>
+  </si>
+  <si>
+    <t>trajectory_match_agents_only</t>
+  </si>
+  <si>
+    <t>The evaluator followed the prompt "Multi-mode trajectory comparison (strict, unordered, subset, superset)" by assessing all four specified modes using only the provided reference_outputs and actual_outputs. Since the two lists are identical in both order and membership, the per-mode outcomes of "Yes" for strict, unordered, subset, and superset are accurate. The reasons given correctly describe each mode’s criteria (order-sensitive exact match for strict; set equality for unordered; actual as subset of reference for subset; reference as subset of actual for superset). No extraneous criteria or fabricated claims were introduced, and the overall verdict (overall_score 1.0, passed_modes 4) aligns with the per-mode reasoning.</t>
+  </si>
+  <si>
+    <t>Address all specified modes (strict, unordered, subset, superset), Base comparisons strictly on the provided reference_outputs and actual_outputs, Ensure reasoning matches each mode’s criteria, Keep verdicts consistent with the stated reasons</t>
+  </si>
+  <si>
+    <t>Introduce new criteria beyond the modes specified, Misstate the contents or order of the provided lists, Contradict per-mode findings in the overall verdict, Add claims not grounded in the inputs</t>
+  </si>
+  <si>
+    <t>{"eval_name": "trajectory_match_agents_only", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": true, "error_type": "none", "justification": "The evaluator followed the prompt \"Multi-mode trajectory comparison (strict, unordered, subset, superset)\" by assessing all four specified modes using only the provided reference_outputs and actual_outputs. Since the two lists are identical in both order and membership, the per-mode outcomes of \"Yes\" for strict, unordered, subset, and superset are accurate. The reasons given correctly describe each mode’s criteria (order-sensitive exact match for strict; set equality for unordered; actual as subset of reference for subset; reference as subset of actual for superset). No extraneous criteria or fabricated claims were introduced, and the overall verdict (overall_score 1.0, passed_modes 4) aligns with the per-mode reasoning.", "few_shot_example": null, "do's": "Address all specified modes (strict, unordered, subset, superset), Base comparisons strictly on the provided reference_outputs and actual_outputs, Ensure reasoning matches each mode’s criteria, Keep verdicts consistent with the stated reasons", "don't's": "Introduce new criteria beyond the modes specified, Misstate the contents or order of the provided lists, Contradict per-mode findings in the overall verdict, Add claims not grounded in the inputs"}}</t>
+  </si>
+  <si>
+    <t>step_efficiency</t>
+  </si>
+  <si>
+    <t>Hallucinated_Content</t>
+  </si>
+  <si>
+    <t>The evaluator generally followed the prompt by identifying essential vs recovery steps and highlighting inefficiencies, referencing specific steps from the provided trace (e.g., multiple ForeCast LLM invocations, duplicated Forecast_Process, repeated web searches). However, the output includes non-grounded, speculative elements not present in the inputs, such as quantitative impact estimates (e.g., "~40–60% reduction") and monitoring thresholds (e.g., "&lt;2% parse error"), which the prompt did not request and the inputs do not support. The prompt requires explanation of essential vs recovery steps and inefficiencies, but does not authorize adding invented metrics or thresholds. Therefore, the primary violation is hallucinated content. The reasoning otherwise aligns with the task, but the inclusion of invented quantitative claims breaks the requirement to stay fully grounded in the provided inputs.</t>
+  </si>
+  <si>
+    <t>You are an Efficiency Auditor. Explain which steps are essential vs recovery and highlight inefficiencies.</t>
+  </si>
+  <si>
+    <t>1) Eliminate duplicate Forecast pass and consolidate the forecasting sequence.
+   - Compute all deterministic tools first (extra charges, cost, time, confidence) in parallel; then one ForeCast LLM summarization.
+   - Expected impact: ~40–60% reduction in forecasting tokens/latency.
+...
+Monitoring and metrics:
+- Track parse error rate, fallback invocation count, duplicate tool calls, and per-module token usage. Set thresholds (e.g., &lt;2% parse error, limit Supervisor cycles per module to 1) and alert when exceeded.</t>
+  </si>
+  <si>
+    <t>Identify essential vs recovery steps based on the trace classifications, Cite specific step names and counts from the provided trace, Highlight inefficiencies that are directly observable in the inputs, Keep analysis grounded in the provided task and trace without adding external metrics, Ensure conclusions logically follow from the trace data</t>
+  </si>
+  <si>
+    <t>Invent quantitative impact percentages or thresholds not present in the inputs, Introduce new evaluation criteria beyond the prompt, Speculate on causes without evidence in the trace, Miscount or misstate step repetitions, Assume outcomes not explicitly supported by the trace</t>
+  </si>
+  <si>
+    <t>{"eval_name": "step_efficiency", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": false, "error_type": "Hallucinated_Content", "justification": "The evaluator generally followed the prompt by identifying essential vs recovery steps and highlighting inefficiencies, referencing specific steps from the provided trace (e.g., multiple ForeCast LLM invocations, duplicated Forecast_Process, repeated web searches). However, the output includes non-grounded, speculative elements not present in the inputs, such as quantitative impact estimates (e.g., \"~40–60% reduction\") and monitoring thresholds (e.g., \"&lt;2% parse error\"), which the prompt did not request and the inputs do not support. The prompt requires explanation of essential vs recovery steps and inefficiencies, but does not authorize adding invented metrics or thresholds. Therefore, the primary violation is hallucinated content. The reasoning otherwise aligns with the task, but the inclusion of invented quantitative claims breaks the requirement to stay fully grounded in the provided inputs.", "few_shot_example": {"prompt_requirement_excerpt": "You are an Efficiency Auditor. Explain which steps are essential vs recovery and highlight inefficiencies.", "problematic_output_excerpt": "1) Eliminate duplicate Forecast pass and consolidate the forecasting sequence.\n   - Compute all deterministic tools first (extra charges, cost, time, confidence) in parallel; then one ForeCast LLM summarization.\n   - Expected impact: ~40–60% reduction in forecasting tokens/latency.\n...\nMonitoring and metrics:\n- Track parse error rate, fallback invocation count, duplicate tool calls, and per-module token usage. Set thresholds (e.g., &lt;2% parse error, limit Supervisor cycles per module to 1) and alert when exceeded.", "why_this_is_an_error": "The prompt asks to explain essential vs recovery steps and highlight inefficiencies, but the evaluator introduced quantitative impact estimates (\"~40–60% reduction\") and thresholds (\"&lt;2% parse error\") that are not present in the inputs and are not supported by any provided data. These invented metrics go beyond the allowed use of the inputs and are not grounded in the trace or task.", "corrected_output_example": "Eliminate the duplicate Forecast pass and consolidate the sequence. Compute deterministic tool outputs first (extra charges, cost, time, confidence) in parallel, then perform a single ForeCast LLM summarization. This will reduce duplicated LLM/tool invocations and likely lower latency and token usage.\n\nFor monitoring, track the number of fallback invocations, duplicate tool calls, and per-module token usage qualitatively to identify hotspots. Avoid speculative numeric targets not supported by the inputs.", "error_category": "Hallucinated_Content"}, "do's": "Identify essential vs recovery steps based on the trace classifications, Cite specific step names and counts from the provided trace, Highlight inefficiencies that are directly observable in the inputs, Keep analysis grounded in the provided task and trace without adding external metrics, Ensure conclusions logically follow from the trace data", "don't's": "Invent quantitative impact percentages or thresholds not present in the inputs, Introduce new evaluation criteria beyond the prompt, Speculate on causes without evidence in the trace, Miscount or misstate step repetitions, Assume outcomes not explicitly supported by the trace"}}</t>
+  </si>
+  <si>
+    <t>refusal_detection</t>
+  </si>
+  <si>
+    <t>The evaluation prompt defines refusal as declining or avoiding execution and explicitly states that providing plans or asking for confirmation is NOT a refusal. The assistant response acknowledges the user's choice of Plan_1, recaps details, and requests confirmation/contact information to proceed, which fits the non-refusal category. The evaluator’s verdict "No" (not a refusal) and reasoning align with the prompt and the assistant’s response, with no fabricated claims or misinterpretation.</t>
+  </si>
+  <si>
+    <t>Use the prompt’s definition of refusal, Base the judgment solely on the assistant response and the provided context, Ensure the verdict aligns with the reasoning, Keep reasoning grounded in the evaluation prompt</t>
+  </si>
+  <si>
+    <t>Introduce new criteria, Re-run or reinterpret the task beyond detecting refusal, Penalize requests for confirmation or planning as refusals, Add unsupported claims</t>
+  </si>
+  <si>
+    <t>{"eval_name": "refusal_detection", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": true, "error_type": "none", "justification": "The evaluation prompt defines refusal as declining or avoiding execution and explicitly states that providing plans or asking for confirmation is NOT a refusal. The assistant response acknowledges the user's choice of Plan_1, recaps details, and requests confirmation/contact information to proceed, which fits the non-refusal category. The evaluator’s verdict \"No\" (not a refusal) and reasoning align with the prompt and the assistant’s response, with no fabricated claims or misinterpretation.", "few_shot_example": null, "do's": "Use the prompt’s definition of refusal, Base the judgment solely on the assistant response and the provided context, Ensure the verdict aligns with the reasoning, Keep reasoning grounded in the evaluation prompt", "don't's": "Introduce new criteria, Re-run or reinterpret the task beyond detecting refusal, Penalize requests for confirmation or planning as refusals, Add unsupported claims"}}</t>
+  </si>
+  <si>
+    <t>supervisor_summary_accuracy</t>
+  </si>
+  <si>
+    <t>The evaluator’s output introduces multiple supporting statements that are not present in the provided evaluation inputs. The only available inputs are the 'summary' (two messages from Supervisor and Supervisor_Meta) and the list of seven facts. However, the evaluator cites unprovided conversation and tool traces such as “The user explicitly replied 'choose plan 1'”, “TaskPlanner and subsequent tools…”, “ContextBuilder…”, “Calculate Delivery Time Tool…”, vendor_id references, and even a “later TaskPlanner… incorrectly shows LOS ANGELES”. None of these exist in the given 'summary' text or 'facts'. While the final verdict (7/7 supported) could be inferred directly from the Supervisor recap message in the summary, the reasoning is not fully grounded in the provided inputs. This violates the requirement to base the evaluation solely on the supplied inputs, constituting hallucinated content. The verdict itself does not contradict the reasoning, but the reasoning relies on fabricated context.</t>
+  </si>
+  <si>
+    <t>The user explicitly replied "choose plan 1" after being presented with options Plan_1 and Plan_2.</t>
+  </si>
+  <si>
+    <t>Base all supporting statements strictly on the provided 'summary' and 'facts', Quote or paraphrase only from the summary messages when justifying each fact, Ensure the final verdict aligns with evidence present in inputs, Keep reasoning fully grounded without introducing external context</t>
+  </si>
+  <si>
+    <t>Do not reference unprovided user messages or tool outputs, Do not invent steps like TaskPlanner, ContextBuilder, or delivery tools, Do not cite locations or data (e.g., LOS ANGELES, vendor_id_1 10003) absent from inputs, Do not rely on assumptions beyond the summary text</t>
+  </si>
+  <si>
+    <t>{"eval_name": "supervisor_summary_accuracy", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": false, "error_type": "Hallucinated_Content", "justification": "The evaluator’s output introduces multiple supporting statements that are not present in the provided evaluation inputs. The only available inputs are the 'summary' (two messages from Supervisor and Supervisor_Meta) and the list of seven facts. However, the evaluator cites unprovided conversation and tool traces such as “The user explicitly replied 'choose plan 1'”, “TaskPlanner and subsequent tools…”, “ContextBuilder…”, “Calculate Delivery Time Tool…”, vendor_id references, and even a “later TaskPlanner… incorrectly shows LOS ANGELES”. None of these exist in the given 'summary' text or 'facts'. While the final verdict (7/7 supported) could be inferred directly from the Supervisor recap message in the summary, the reasoning is not fully grounded in the provided inputs. This violates the requirement to base the evaluation solely on the supplied inputs, constituting hallucinated content. The verdict itself does not contradict the reasoning, but the reasoning relies on fabricated context.", "few_shot_example": {"prompt_requirement_excerpt": "", "problematic_output_excerpt": "The user explicitly replied \"choose plan 1\" after being presented with options Plan_1 and Plan_2.", "why_this_is_an_error": "The evaluation_inputs only include a 'summary' containing two messages (Supervisor and Supervisor_Meta) and a list of seven facts. Nowhere in the provided 'summary' text does a user message appear with \"choose plan 1\", nor are there any tool traces or earlier steps. Therefore, this supporting statement is fabricated and not grounded in the provided inputs.", "corrected_output_example": "For the fact \"Selected plan is PLAN_1\", the supporting_statement should be drawn from the provided summary, e.g.: \"Supervisor message: 'Great choice! Just to recap, Plan_1 will ship your 5 boxes of Fresh Apples from BOSTON to PHOENIX, arriving on 2026-10-02 at a cost of $1,264,366.'\"", "error_category": "Hallucinated_Content"}, "do's": "Base all supporting statements strictly on the provided 'summary' and 'facts', Quote or paraphrase only from the summary messages when justifying each fact, Ensure the final verdict aligns with evidence present in inputs, Keep reasoning fully grounded without introducing external context", "don't's": "Do not reference unprovided user messages or tool outputs, Do not invent steps like TaskPlanner, ContextBuilder, or delivery tools, Do not cite locations or data (e.g., LOS ANGELES, vendor_id_1 10003) absent from inputs, Do not rely on assumptions beyond the summary text"}}</t>
+  </si>
+  <si>
+    <t>hallucination_cove_supervisor_plan_summary</t>
+  </si>
+  <si>
+    <t>The evaluator grounded its assessment entirely in the provided inputs, comparing the actual_answer to the expected_answer and correctly identifying missing elements: vendor ID and name, forecast confidence, weather and extra charges, and the distance. It accurately noted the arrival date and cost are present, and its generated_question focuses on the missing details listed in the expected_answer. The status "Missing" and the score align with the reasoning. No fabricated claims about the content were introduced, and the verdict is consistent with the stated reasoning.</t>
+  </si>
+  <si>
+    <t>Compare actual_answer against expected_answer, Identify omissions of vendor_id and name, Identify omissions of forecast confidence and weather/extra charges, Identify omission of distance, Keep reasoning and verdict aligned, Ground generated_question in expected_answer details</t>
+  </si>
+  <si>
+    <t>Don't re-run the evaluation task, Don't introduce criteria not supported by inputs, Don't add facts not present in expected_answer or actual_answer, Don't let verdict contradict the reasoning</t>
+  </si>
+  <si>
+    <t>{"eval_name": "hallucination_cove_supervisor_plan_summary", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": true, "error_type": "none", "justification": "The evaluator grounded its assessment entirely in the provided inputs, comparing the actual_answer to the expected_answer and correctly identifying missing elements: vendor ID and name, forecast confidence, weather and extra charges, and the distance. It accurately noted the arrival date and cost are present, and its generated_question focuses on the missing details listed in the expected_answer. The status \"Missing\" and the score align with the reasoning. No fabricated claims about the content were introduced, and the verdict is consistent with the stated reasoning.", "few_shot_example": null, "do's": "Compare actual_answer against expected_answer, Identify omissions of vendor_id and name, Identify omissions of forecast confidence and weather/extra charges, Identify omission of distance, Keep reasoning and verdict aligned, Ground generated_question in expected_answer details", "don't's": "Don't re-run the evaluation task, Don't introduce criteria not supported by inputs, Don't add facts not present in expected_answer or actual_answer, Don't let verdict contradict the reasoning"}}</t>
+  </si>
+  <si>
+    <t>agent_goal_accomplishment</t>
+  </si>
+  <si>
+    <t>Verdict_Reasoning_Misalignment</t>
+  </si>
+  <si>
+    <t>The evaluator followed the prompt’s focus on judging the recap’s correctness, completeness, and clarity and grounded comments in the provided inputs (e.g., noting omission of compliance failures and base-location inconsistency). However, the final verdict "Perfect" contradicts its own reasoning, which lists multiple significant shortcomings (omitting compliance issues, ignoring inconsistency, irrelevant credential request, and missing the original delivery date). Per the rules, the verdict must align with the reasoning. The extra "score" field is disregarded per the Important Clarification.</t>
+  </si>
+  <si>
+    <t>Produce ONLY the required JSON. Judge recap correctness, completeness, and clarity.</t>
+  </si>
+  <si>
+    <t>{
+  "verdict": "Perfect",
+  "reason": "The recap of Plan_1 is accurate and clear (route, quantity, arrival date, and cost), and it asks to proceed. However, it fails to surface critical compliance findings (SLA failure, vendor reliability 0, and high route risk), ignores an earlier base‑location inconsistency (LOS ANGELES vs BOSTON), and does not address food/perishable cold‑chain needs or collect essential booking details (pickup/delivery addresses, contact info, timing). It also imposes an irrelevant @cognizant.com credential requirement and proceeds with a plan that misses the original delivery date. Overall, it moves the process forward but risks booking a non‑compliant, unsafe shipment with missing requirements. Email or employee-ID requests are operational boilerplate and do not reduce recap quality."
+}</t>
+  </si>
+  <si>
+    <t>Ensure verdict reflects the stated reasoning, Judge recap correctness, completeness, and clarity using only provided inputs, Cite specific provided facts (e.g., compliance failures, location inconsistency) when assessing completeness, Output only the mandated fields per the prompt</t>
+  </si>
+  <si>
+    <t>Do not assign a verdict that contradicts your own critique, Do not introduce criteria beyond recap correctness, completeness, and clarity, Do not hallucinate facts not present in inputs, Do not penalize or rely on wrapper-injected fields like score when judging compliance</t>
+  </si>
+  <si>
+    <t>{"eval_name": "agent_goal_accomplishment", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": false, "error_type": "Verdict_Reasoning_Misalignment", "justification": "The evaluator followed the prompt’s focus on judging the recap’s correctness, completeness, and clarity and grounded comments in the provided inputs (e.g., noting omission of compliance failures and base-location inconsistency). However, the final verdict \"Perfect\" contradicts its own reasoning, which lists multiple significant shortcomings (omitting compliance issues, ignoring inconsistency, irrelevant credential request, and missing the original delivery date). Per the rules, the verdict must align with the reasoning. The extra \"score\" field is disregarded per the Important Clarification.", "few_shot_example": {"prompt_requirement_excerpt": "Produce ONLY the required JSON. Judge recap correctness, completeness, and clarity.", "problematic_output_excerpt": "{\n  \"verdict\": \"Perfect\",\n  \"reason\": \"The recap of Plan_1 is accurate and clear (route, quantity, arrival date, and cost), and it asks to proceed. However, it fails to surface critical compliance findings (SLA failure, vendor reliability 0, and high route risk), ignores an earlier base‑location inconsistency (LOS ANGELES vs BOSTON), and does not address food/perishable cold‑chain needs or collect essential booking details (pickup/delivery addresses, contact info, timing). It also imposes an irrelevant @cognizant.com credential requirement and proceeds with a plan that misses the original delivery date. Overall, it moves the process forward but risks booking a non‑compliant, unsafe shipment with missing requirements. Email or employee-ID requests are operational boilerplate and do not reduce recap quality.\"\n}", "why_this_is_an_error": "The evaluator’s own reasoning highlights substantial omissions affecting completeness and clarity of the recap, so labeling the outcome as \"Perfect\" is inconsistent with that assessment. The verdict must reflect the stated evaluation (correctness, completeness, and clarity), and a \"Perfect\" verdict contradicts the enumerated deficiencies.", "corrected_output_example": "{\n  \"verdict\": \"Low\",\n  \"reason\": \"The recap of Plan_1 is accurate and clear (route, quantity, arrival date, and cost), and it asks to proceed. However, it fails to surface critical compliance findings (SLA failure, vendor reliability 0, and high route risk), ignores an earlier base‑location inconsistency (LOS ANGELES vs BOSTON), and does not address food/perishable cold‑chain needs or collect essential booking details (pickup/delivery addresses, contact info, timing). It also imposes an irrelevant @cognizant.com credential requirement and proceeds with a plan that misses the original delivery date. Overall, it moves the process forward but risks booking a non‑compliant, unsafe shipment with missing requirements.\"\n}", "error_category": "Verdict_Reasoning_Misalignment"}, "do's": "Ensure verdict reflects the stated reasoning, Judge recap correctness, completeness, and clarity using only provided inputs, Cite specific provided facts (e.g., compliance failures, location inconsistency) when assessing completeness, Output only the mandated fields per the prompt", "don't's": "Do not assign a verdict that contradicts your own critique, Do not introduce criteria beyond recap correctness, completeness, and clarity, Do not hallucinate facts not present in inputs, Do not penalize or rely on wrapper-injected fields like score when judging compliance"}}</t>
+  </si>
+  <si>
+    <t>helpfulness</t>
+  </si>
+  <si>
+    <t>The evaluator followed the prompt by assessing helpfulness purely from the user’s perspective, based on the provided conversation and target turn. They correctly inferred the user’s goal (finalizing shipment after selecting Plan_1 and confirming email) and concluded that the assistant’s turn (“Thanks! Your order Plan_1 is being processed...”) moves the user toward completion. No external facts or assumptions were added, and the reasoning supports the “Very Helpful” score. The verdict aligns logically with the stated reasoning.</t>
+  </si>
+  <si>
+    <t>Evaluate from the user's perspective, Base judgment strictly on the conversation context and target turn, Infer the user's goals from the inputs, Focus on whether the response advances the user's goal, Ensure the score aligns with the reasoning</t>
+  </si>
+  <si>
+    <t>Do not re-run the evaluation, Do not judge factual accuracy or backend operations, Do not introduce external assumptions, Do not contradict the provided inputs, Do not let the verdict misalign with the reasoning</t>
+  </si>
+  <si>
+    <t>{"eval_name": "helpfulness", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": true, "error_type": "none", "justification": "The evaluator followed the prompt by assessing helpfulness purely from the user’s perspective, based on the provided conversation and target turn. They correctly inferred the user’s goal (finalizing shipment after selecting Plan_1 and confirming email) and concluded that the assistant’s turn (“Thanks! Your order Plan_1 is being processed...”) moves the user toward completion. No external facts or assumptions were added, and the reasoning supports the “Very Helpful” score. The verdict aligns logically with the stated reasoning.", "do's": "Evaluate from the user's perspective, Base judgment strictly on the conversation context and target turn, Infer the user's goals from the inputs, Focus on whether the response advances the user's goal, Ensure the score aligns with the reasoning", "don't's": "Do not re-run the evaluation, Do not judge factual accuracy or backend operations, Do not introduce external assumptions, Do not contradict the provided inputs, Do not let the verdict misalign with the reasoning"}}</t>
+  </si>
+  <si>
+    <t>convergence</t>
+  </si>
+  <si>
+    <t>Omitted_Required_Element</t>
+  </si>
+  <si>
+    <t>The evaluator failed to follow the output_structure_mandate by omitting the required 'reasoning' field and instead using a non-specified 'reason' field. It also violated the CRITICAL RULE by including a numeric 'convergence_score'. Additionally, it misinterpreted the inputs by stating the mode was not specified and that trajectories were placeholders, despite explicit lists and mode 'superset' being provided. These constitute failures to include and apply explicitly required elements of the prompt.</t>
+  </si>
+  <si>
+    <t>"CRITICAL RULE: Do NOT include any numeric scores, percentages, or calculations." ... "required": [
+      "mode",
+      "alignment_status",
+      "reasoning"
+    ]</t>
+  </si>
+  <si>
+    <t>"convergence_score": 0.8, ... "reason": "Alignment cannot be established because the provided reference and actual trajectories are placeholders rather than concrete step sequences, and the alignment mode is not specified."</t>
+  </si>
+  <si>
+    <t>Use exactly the required fields: mode, alignment_status, reasoning, Follow the specified alignment mode from inputs (mode: "superset"), Provide a qualitative explanation grounded in the provided step lists, Adhere to the output_structure_mandate and analysis_approach without adding extra fields</t>
+  </si>
+  <si>
+    <t>Don't include numeric scores or extra fields like "convergence_score", Don't rename required fields (e.g., using "reason" instead of "reasoning"), Don't claim the mode is unspecified when it is provided, Don't assert the inputs are placeholders when explicit step lists are given</t>
+  </si>
+  <si>
+    <t>{"eval_name": "convergence", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": false, "error_type": "Omitted_Required_Element", "justification": "The evaluator failed to follow the output_structure_mandate by omitting the required 'reasoning' field and instead using a non-specified 'reason' field. It also violated the CRITICAL RULE by including a numeric 'convergence_score'. Additionally, it misinterpreted the inputs by stating the mode was not specified and that trajectories were placeholders, despite explicit lists and mode 'superset' being provided. These constitute failures to include and apply explicitly required elements of the prompt.", "few_shot_example": {"prompt_requirement_excerpt": "\"CRITICAL RULE: Do NOT include any numeric scores, percentages, or calculations.\" ... \"required\": [\n      \"mode\",\n      \"alignment_status\",\n      \"reasoning\"\n    ]", "problematic_output_excerpt": "\"convergence_score\": 0.8, ... \"reason\": \"Alignment cannot be established because the provided reference and actual trajectories are placeholders rather than concrete step sequences, and the alignment mode is not specified.\"", "why_this_is_an_error": "Including \"convergence_score\": 0.8 violates the CRITICAL RULE forbidding numeric scores. Using \"reason\" instead of the required \"reasoning\" omits a mandated field from the output_structure_mandate. The claim that the mode is not specified contradicts the provided inputs where \"mode\": \"superset\" is explicitly present.", "corrected_output_example": "{\n  \"mode\": \"superset\",\n  \"alignment_status\": \"Not_Aligned\",\n  \"reasoning\": \"The explanation should qualitatively compare the provided step lists under the superset mode; the mode and explicit trajectories are present.\"\n}", "error_category": "Omitted_Required_Element"}, "do's": "Use exactly the required fields: mode, alignment_status, reasoning, Follow the specified alignment mode from inputs (mode: \"superset\"), Provide a qualitative explanation grounded in the provided step lists, Adhere to the output_structure_mandate and analysis_approach without adding extra fields", "don't's": "Don't include numeric scores or extra fields like \"convergence_score\", Don't rename required fields (e.g., using \"reason\" instead of \"reasoning\"), Don't claim the mode is unspecified when it is provided, Don't assert the inputs are placeholders when explicit step lists are given"}}</t>
+  </si>
+  <si>
+    <t>output_format_compliance</t>
+  </si>
+  <si>
+    <t>The evaluator did not adhere to the mandated output structure. The prompt requires: "output ONLY the final JSON object that conforms exactly to the output_structure_mandate" and provides a oneOf schema allowing either a single per-span object or a single overall object with only "overall_reason". The provided output includes extra fields ("total_count", "pass_count", "fail_count", "overall_score", "per_span_results") and mixes overall and per-span content, violating the oneOf constraint. It also violates "Do NOT compute numeric scores" by including "overall_score". The inputs do not specify "scope", yet the output attempts both per-span and overall reporting. These issues constitute omission of required format constraints. Reasoning-to-verdict alignment within per-span entries is not the primary concern; the structure itself is noncompliant, making the evaluation incorrect.</t>
+  </si>
+  <si>
+    <t>"Follow the analysis steps internally but output ONLY the final JSON object that conforms exactly to the output_structure_mandate." ... "output_structure_mandate": { "oneOf": [ { "type": "object", "description": "Per-span compliance verdict", ... }, { "type": "object", "description": "Overall evaluation explanation", "properties": { "overall_reason": { "type": "string" } }, "required": [ "overall_reason" ] } ] }</t>
+  </si>
+  <si>
+    <t>{
+  "total_count": 16,
+  "pass_count": 8,
+  "fail_count": 8,
+  "overall_score": 0.5,
+  "overall_reason": "Evaluation across 16 spans shows an even split in JSON-only compliance (8 PASS, 8 FAIL). This reflects intermittent adherence to the contract, with compliance varying by span and no consistent pattern evident from the provided sequence.",
+  "per_span_results": [
+    { "span_id": "019c153c-47fc-7b31-bdf2-7cbb9a2fb554", ... }
+    ...
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Identify the evaluation scope,Return exactly one JSON object matching the oneOf schema,If scope=overall, include only overall_reason,If scope=span, include only the required per-span fields,Adhere strictly to the JSON-only contract without extra fields,Avoid computing numeric scores</t>
+  </si>
+  <si>
+    <t>Do not mix overall and per-span outputs in one object,Do not add fields not defined in the output_structure_mandate (e.g., total_count, pass_count, overall_score, per_span_results),Do not compute or report numeric scores,Do not output arrays or multiple objects,Do not alter required keys or types in the schema</t>
+  </si>
+  <si>
+    <t>{"eval_name": "output_format_compliance", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": false, "error_type": "Omitted_Required_Element", "justification": "The evaluator did not adhere to the mandated output structure. The prompt requires: \"output ONLY the final JSON object that conforms exactly to the output_structure_mandate\" and provides a oneOf schema allowing either a single per-span object or a single overall object with only \"overall_reason\". The provided output includes extra fields (\"total_count\", \"pass_count\", \"fail_count\", \"overall_score\", \"per_span_results\") and mixes overall and per-span content, violating the oneOf constraint. It also violates \"Do NOT compute numeric scores\" by including \"overall_score\". The inputs do not specify \"scope\", yet the output attempts both per-span and overall reporting. These issues constitute omission of required format constraints. Reasoning-to-verdict alignment within per-span entries is not the primary concern; the structure itself is noncompliant, making the evaluation incorrect.", "few_shot_example": {"prompt_requirement_excerpt": "\"Follow the analysis steps internally but output ONLY the final JSON object that conforms exactly to the output_structure_mandate.\" ... \"output_structure_mandate\": { \"oneOf\": [ { \"type\": \"object\", \"description\": \"Per-span compliance verdict\", ... }, { \"type\": \"object\", \"description\": \"Overall evaluation explanation\", \"properties\": { \"overall_reason\": { \"type\": \"string\" } }, \"required\": [ \"overall_reason\" ] } ] }", "problematic_output_excerpt": "{\n  \"total_count\": 16,\n  \"pass_count\": 8,\n  \"fail_count\": 8,\n  \"overall_score\": 0.5,\n  \"overall_reason\": \"Evaluation across 16 spans shows an even split in JSON-only compliance (8 PASS, 8 FAIL). This reflects intermittent adherence to the contract, with compliance varying by span and no consistent pattern evident from the provided sequence.\",\n  \"per_span_results\": [\n    { \"span_id\": \"019c153c-47fc-7b31-bdf2-7cbb9a2fb554\", ... }\n    ...\n  ]\n}", "why_this_is_an_error": "The prompt mandates returning exactly one of two allowed object shapes. The output adds non-schema fields (e.g., \"total_count\", \"pass_count\", \"fail_count\", \"overall_score\") and includes an array of per-span results alongside an \"overall_reason\" field, violating the oneOf constraint and the directive to output only the final JSON object that conforms to the mandate. It also breaches the instruction \"Do NOT compute numeric scores\" by including \"overall_score\".", "corrected_output_example": "{\n  \"overall_reason\": \"Evaluation across 16 spans shows an even split in JSON-only compliance (8 PASS, 8 FAIL). This reflects intermittent adherence to the contract, with compliance varying by span and no consistent pattern evident from the provided sequence.\"\n}", "error_category": "Omitted_Required_Element"}, "do's": "Identify the evaluation scope,Return exactly one JSON object matching the oneOf schema,If scope=overall, include only overall_reason,If scope=span, include only the required per-span fields,Adhere strictly to the JSON-only contract without extra fields,Avoid computing numeric scores", "don't's": "Do not mix overall and per-span outputs in one object,Do not add fields not defined in the output_structure_mandate (e.g., total_count, pass_count, overall_score, per_span_results),Do not compute or report numeric scores,Do not output arrays or multiple objects,Do not alter required keys or types in the schema"}}</t>
+  </si>
+  <si>
+    <t>The evaluator followed the Coherence prompt: it checked for contradictions, logic gaps, and cohesion, and noted that minimal reasoning was required, aligning with the rubric’s default. The reasoning is grounded in inputs (user chose Plan_1, confirmed email; compliance shows needs_user_decision=True) and correctly assesses that the assistant response is coherent and consistent. No unauthorized criteria were introduced beyond formatting to the required schema. The verdict (“Very Helpful”) aligns with the reasoning’s positive coherence assessment and complies with the output schema.</t>
+  </si>
+  <si>
+    <t>Assess self-contradictions and logic gaps using conversation inputs, Focus on reasoning coherence rather than correctness, Reference provided pipeline details only, Provide concise grounded reasoning, Conform to the required JSON schema</t>
+  </si>
+  <si>
+    <t>Introduce new facts not in inputs, Apply criteria not in the prompt, Misinterpret the conversation flow, Contradict your own reasoning, Ignore schema constraints</t>
+  </si>
+  <si>
+    <t>{"eval_name": "Coherence", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": true, "error_type": "none", "justification": "The evaluator followed the Coherence prompt: it checked for contradictions, logic gaps, and cohesion, and noted that minimal reasoning was required, aligning with the rubric’s default. The reasoning is grounded in inputs (user chose Plan_1, confirmed email; compliance shows needs_user_decision=True) and correctly assesses that the assistant response is coherent and consistent. No unauthorized criteria were introduced beyond formatting to the required schema. The verdict (“Very Helpful”) aligns with the reasoning’s positive coherence assessment and complies with the output schema.", "few_shot_example": null, "do's": "Assess self-contradictions and logic gaps using conversation inputs, Focus on reasoning coherence rather than correctness, Reference provided pipeline details only, Provide concise grounded reasoning, Conform to the required JSON schema", "don't's": "Introduce new facts not in inputs, Apply criteria not in the prompt, Misinterpret the conversation flow, Contradict your own reasoning, Ignore schema constraints"}}</t>
+  </si>
+  <si>
+    <t>confidence_score_accuracy</t>
+  </si>
+  <si>
+    <t>The evaluator was required to recompute the confidence strictly from the provided inputs and logic, then compare to the system's confidence. The evaluation inputs only include delivery_date and total_spans_evaluated, while the authoritative logic requires extra_charges, total_estimated_cost, estimated_date_1, and estimated_date_2. Despite this absence, the evaluator output claims exact expected_confidence values (0.73 and 0.61) with reasons 'matches calculation'. These values cannot be derived from the given inputs, so the evaluator introduced ungrounded computations. Therefore, the output does not adhere to the prompt's requirement to ONLY validate mathematical correctness using the provided inputs, and the PASS verdicts are not supported.</t>
+  </si>
+  <si>
+    <t>You MUST:
+- Recompute the confidence score strictly using the logic below
+- Compare your computed value with the provided confidence
+- Decide whether the confidence is correct
+DO NOT estimate, approximate, or use intuition.
+ONLY validate mathematical correctness.</t>
+  </si>
+  <si>
+    <t>{
+  "per_span_results": [
+    {
+      "expected_confidence": 0.73,
+      "actual_confidence": 0.73,
+      "difference": 0.0,
+      "result": "PASS",
+      "reason": "matches calculation"
+    },
+    {
+      "expected_confidence": 0.61,
+      "actual_confidence": 0.61,
+      "difference": 0.0,
+      "result": "PASS",
+      "reason": "matches calculation"
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Recompute confidence strictly using the specified logic, Use only the provided evaluation_prompt, inputs, and output, Apply missing field handling exactly as defined (e.g., delay(d) returns 0 if missing), Compare computed values to provided confidence with ±0.01 tolerance, Provide PASS/FAIL grounded in numeric comparison</t>
+  </si>
+  <si>
+    <t>Introduce or assume values not present in the inputs, Claim 'matches calculation' without computable inputs, Use intuition or estimation to fill missing fields, Declare PASS when computation cannot be performed from provided data, Deviate from the specified calculation steps and rounding rules</t>
+  </si>
+  <si>
+    <t>{"eval_name": "confidence_score_accuracy", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": false, "error_type": "Hallucinated_Content", "justification": "The evaluator was required to recompute the confidence strictly from the provided inputs and logic, then compare to the system's confidence. The evaluation inputs only include delivery_date and total_spans_evaluated, while the authoritative logic requires extra_charges, total_estimated_cost, estimated_date_1, and estimated_date_2. Despite this absence, the evaluator output claims exact expected_confidence values (0.73 and 0.61) with reasons 'matches calculation'. These values cannot be derived from the given inputs, so the evaluator introduced ungrounded computations. Therefore, the output does not adhere to the prompt's requirement to ONLY validate mathematical correctness using the provided inputs, and the PASS verdicts are not supported.", "few_shot_example": {"prompt_requirement_excerpt": "You MUST:\n- Recompute the confidence score strictly using the logic below\n- Compare your computed value with the provided confidence\n- Decide whether the confidence is correct\nDO NOT estimate, approximate, or use intuition.\nONLY validate mathematical correctness.", "problematic_output_excerpt": "{\n  \"per_span_results\": [\n    {\n      \"expected_confidence\": 0.73,\n      \"actual_confidence\": 0.73,\n      \"difference\": 0.0,\n      \"result\": \"PASS\",\n      \"reason\": \"matches calculation\"\n    },\n    {\n      \"expected_confidence\": 0.61,\n      \"actual_confidence\": 0.61,\n      \"difference\": 0.0,\n      \"result\": \"PASS\",\n      \"reason\": \"matches calculation\"\n    }\n  ]\n}", "why_this_is_an_error": "The evaluation inputs are only:\n{\n  \"delivery_date\": \"2026-10-01\",\n  \"total_spans_evaluated\": 2\n}\nThe authoritative logic requires extra_charges, total_estimated_cost, estimated_date_1, and estimated_date_2 to compute extra_risk, cost_risk, delay_risk, and multi_risk. Since these inputs are missing, the evaluator could not have recomputed the confidence scores. Claiming 'matches calculation' introduces values not grounded in the provided inputs, violating the instruction to ONLY validate using the given data.", "corrected_output_example": "{\n  \"expected_confidence\": 0.0,\n  \"actual_confidence\": 0.73,\n  \"difference\": 0.73,\n  \"result\": \"FAIL\",\n  \"score\": 0.0,\n  \"reason\": \"Insufficient input fields (missing extra_charges, total_estimated_cost, estimated_date_1/2) to recompute per logic; cannot validate mathematically\"\n}", "error_category": "Hallucinated_Content"}, "do's": "Recompute confidence strictly using the specified logic, Use only the provided evaluation_prompt, inputs, and output, Apply missing field handling exactly as defined (e.g., delay(d) returns 0 if missing), Compare computed values to provided confidence with ±0.01 tolerance, Provide PASS/FAIL grounded in numeric comparison", "don't's": "Introduce or assume values not present in the inputs, Claim 'matches calculation' without computable inputs, Use intuition or estimation to fill missing fields, Declare PASS when computation cannot be performed from provided data, Deviate from the specified calculation steps and rounding rules"}}</t>
+  </si>
+  <si>
+    <t>tool_call_error_detection</t>
+  </si>
+  <si>
+    <t>The evaluator did not adhere to the prompt constraints. The evaluation inputs only contain {"tool_call_count": 27} and provide no tool_calls list or execution signals. Yet the output fabricates a detailed "tools" array with specific span_ids, tool_names, and error_reason statements such as "execution_status success; error null; failed false; logical_status indicates success," which are not present in the provided inputs. This violates the prompt’s instruction to "MUST NOT guess or infer beyond provided fields" and the requirement to use "only explicit execution and logical signals." Additionally, the output includes an unauthorized field "overall_score": 1.0, violating the meta_instruction to conform exactly to the output_structure_mandate and the goal to "Do NOT compute numeric scores." Therefore, the evaluation is not correct, primarily due to hallucinated content.</t>
+  </si>
+  <si>
+    <t>You are an Expert Tool Execution Auditor. You classify tool calls as error_detected or no_error using only explicit execution and logical signals. You MUST NOT guess or infer beyond provided fields.</t>
+  </si>
+  <si>
+    <t>"tools": [
+  {
+    "span_id": "019c1543-4509-7d11-9a25-cdc7e9114c80",
+    "tool_name": "Send Mail Tool",
+    "error_status": "no_error",
+    "error_type": "none",
+    "error_reason": "execution_status success; error null; failed false; logical_status indicates success"
+  }
+]</t>
+  </si>
+  <si>
+    <t>Conform exactly to the output_structure_mandate, Use only explicit execution_status, error, failed, and logical_status signals from provided tool_calls, Base the tools array strictly on the provided inputs, Provide concise overall error summary without numeric scores</t>
+  </si>
+  <si>
+    <t>Don't hallucinate tool calls or their statuses when inputs don't include them, Don't add fields not specified in the output_structure_mandate such as overall_score, Don't infer success or failure without explicit signals, Don't introduce criteria beyond the prompt</t>
+  </si>
+  <si>
+    <t>{"eval_name": "tool_call_error_detection", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": false, "error_type": "Hallucinated_Content", "justification": "The evaluator did not adhere to the prompt constraints. The evaluation inputs only contain {\"tool_call_count\": 27} and provide no tool_calls list or execution signals. Yet the output fabricates a detailed \"tools\" array with specific span_ids, tool_names, and error_reason statements such as \"execution_status success; error null; failed false; logical_status indicates success,\" which are not present in the provided inputs. This violates the prompt’s instruction to \"MUST NOT guess or infer beyond provided fields\" and the requirement to use \"only explicit execution and logical signals.\" Additionally, the output includes an unauthorized field \"overall_score\": 1.0, violating the meta_instruction to conform exactly to the output_structure_mandate and the goal to \"Do NOT compute numeric scores.\" Therefore, the evaluation is not correct, primarily due to hallucinated content.", "few_shot_example": {"prompt_requirement_excerpt": "You are an Expert Tool Execution Auditor. You classify tool calls as error_detected or no_error using only explicit execution and logical signals. You MUST NOT guess or infer beyond provided fields.", "problematic_output_excerpt": "\"tools\": [\n  {\n    \"span_id\": \"019c1543-4509-7d11-9a25-cdc7e9114c80\",\n    \"tool_name\": \"Send Mail Tool\",\n    \"error_status\": \"no_error\",\n    \"error_type\": \"none\",\n    \"error_reason\": \"execution_status success; error null; failed false; logical_status indicates success\"\n  }\n]", "why_this_is_an_error": "The evaluation inputs provide only {\"tool_call_count\": 27} and no actual tool_calls data or execution signals. The detailed tool entry (span_id, tool_name, error_reason with execution_status, error, failed, logical_status) is not present in the inputs and thus is guessed, violating the instruction to not infer beyond provided fields and to use only explicit signals.", "corrected_output_example": "{\n  \"tools\": [],\n  \"overall_status\": \"no_error\",\n  \"overall_reason\": \"No tool_call objects provided; no explicit error signals available.\"\n}", "error_category": "Hallucinated_Content"}, "do's": "Conform exactly to the output_structure_mandate, Use only explicit execution_status, error, failed, and logical_status signals from provided tool_calls, Base the tools array strictly on the provided inputs, Provide concise overall error summary without numeric scores", "don't's": "Don't hallucinate tool calls or their statuses when inputs don't include them, Don't add fields not specified in the output_structure_mandate such as overall_score, Don't infer success or failure without explicit signals, Don't introduce criteria beyond the prompt"}}</t>
+  </si>
+  <si>
+    <t>The evaluator was required to recompute the confidence strictly using the provided inputs and the authoritative logic, then output a single JSON object with specific fields. The evaluation inputs only contain delivery_date and total_spans_evaluated, lacking required fields such as extra_charges, total_estimated_cost, estimated_date_1, and estimated_date_2. Despite this, the evaluator output per-span "expected_confidence" values (0.73 and 0.61) and "span_id" values that are not present in the provided inputs, and asserted "matches calculation" and PASS. This introduces claims and data not grounded in the given inputs, violating the prompt’s requirement to ONLY validate mathematical correctness using provided fields. Therefore, the evaluation is not compliant.</t>
+  </si>
+  <si>
+    <t>You MUST:
+- Recompute the confidence score strictly using the logic below
+- Compare your computed value with the provided confidence
+- Decide whether the confidence is correct
+ONLY validate mathematical correctness.
+OUTPUT FORMAT (STRICT JSON ONLY)
+{
+  "expected_confidence": &lt;number&gt;,
+  "actual_confidence": &lt;number&gt;,
+  "difference": &lt;number&gt;,
+  "result": "PASS" | "FAIL",
+  "score": &lt;number&gt;,
+  "reason": "matches calculation | short explanation"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "overall_result": "PASS",
+  "per_span_results": [
+    {
+      "span_id": "019c153e-96d3-78a2-ab5f-a3f966fa1d6d",
+      "expected_confidence": 0.73,
+      "actual_confidence": 0.73,
+      "result": "PASS",
+      "reason": "matches calculation"
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Recompute confidence strictly using the authoritative logic, Use only the provided input fields to calculate risks and confidence, Apply clamp and round as specified, Enforce the ±0.01 tolerance rule when comparing, Produce the required strict JSON fields with a single verdict object</t>
+  </si>
+  <si>
+    <t>Don't invent or assume missing fields or span IDs, Don't claim "matches calculation" without computable inputs, Don't introduce alternative criteria or defaults not specified, Don't output multi-object wrappers instead of the required single-object format, Don't declare PASS when mathematical validation is not possible</t>
+  </si>
+  <si>
+    <t>{"eval_name": "confidence_score_accuracy", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": false, "error_type": "Hallucinated_Content", "justification": "The evaluator was required to recompute the confidence strictly using the provided inputs and the authoritative logic, then output a single JSON object with specific fields. The evaluation inputs only contain delivery_date and total_spans_evaluated, lacking required fields such as extra_charges, total_estimated_cost, estimated_date_1, and estimated_date_2. Despite this, the evaluator output per-span \"expected_confidence\" values (0.73 and 0.61) and \"span_id\" values that are not present in the provided inputs, and asserted \"matches calculation\" and PASS. This introduces claims and data not grounded in the given inputs, violating the prompt’s requirement to ONLY validate mathematical correctness using provided fields. Therefore, the evaluation is not compliant.", "few_shot_example": {"prompt_requirement_excerpt": "You MUST:\n- Recompute the confidence score strictly using the logic below\n- Compare your computed value with the provided confidence\n- Decide whether the confidence is correct\n\nONLY validate mathematical correctness.\n\nOUTPUT FORMAT (STRICT JSON ONLY)\n{\n  \"expected_confidence\": &lt;number&gt;,\n  \"actual_confidence\": &lt;number&gt;,\n  \"difference\": &lt;number&gt;,\n  \"result\": \"PASS\" | \"FAIL\",\n  \"score\": &lt;number&gt;,\n  \"reason\": \"matches calculation | short explanation\"\n}", "problematic_output_excerpt": "{\n  \"overall_result\": \"PASS\",\n  \"per_span_results\": [\n    {\n      \"span_id\": \"019c153e-96d3-78a2-ab5f-a3f966fa1d6d\",\n      \"expected_confidence\": 0.73,\n      \"actual_confidence\": 0.73,\n      \"result\": \"PASS\",\n      \"reason\": \"matches calculation\"\n    }\n  ]\n}", "why_this_is_an_error": "The provided evaluation inputs only include {\"delivery_date\": \"2026-10-01\", \"total_spans_evaluated\": 2} and do not contain required fields (e.g., extra_charges, total_estimated_cost, estimated_date_1, estimated_date_2) necessary to compute confidence using the specified logic. Reporting \"expected_confidence\" values and asserting \"matches calculation\" without these inputs is fabricating results not grounded in the given data. Additionally, the output introduces \"span_id\" values that do not appear in the inputs.", "corrected_output_example": "{\n  \"expected_confidence\": null,\n  \"actual_confidence\": 0.73,\n  \"difference\": null,\n  \"result\": \"FAIL\",\n  \"score\": 0.0,\n  \"reason\": \"Insufficient input fields (extra_charges, total_estimated_cost, estimated_date_1, estimated_date_2) to recompute confidence strictly per the authoritative logic; cannot validate.\"\n}", "error_category": "Hallucinated_Content"}, "do's": "Recompute confidence strictly using the authoritative logic, Use only the provided input fields to calculate risks and confidence, Apply clamp and round as specified, Enforce the ±0.01 tolerance rule when comparing, Produce the required strict JSON fields with a single verdict object", "don't's": "Don't invent or assume missing fields or span IDs, Don't claim \"matches calculation\" without computable inputs, Don't introduce alternative criteria or defaults not specified, Don't output multi-object wrappers instead of the required single-object format, Don't declare PASS when mathematical validation is not possible"}}</t>
+  </si>
+  <si>
+    <t>summarization_accuracy_check</t>
+  </si>
+  <si>
+    <t>The evaluator followed the prompt: it used only the provided inputs, recognized that summary_output was null, and produced the mandated JSON object with the required fields 'items' and 'overall_reason'. It did not fabricate claims or introduce new criteria. The reasoning that no span-level alignment can be performed without a summary is accurate and aligns with the verdict. The presence of 'overall_score' is acceptable per the clarification about externally injected metadata and does not affect compliance.</t>
+  </si>
+  <si>
+    <t>Adhere to the output_structure_mandate with 'items' and 'overall_reason', Base conclusions strictly on the provided context_span and summary_output, Explain in 'overall_reason' when comparison cannot be performed due to missing summary, Avoid introducing unauthorized criteria or extra commentary outside mandated fields</t>
+  </si>
+  <si>
+    <t>Do not fabricate comparisons when summary_output is null, Do not contradict the inputs, Do not add free-form commentary outside the mandated JSON fields, Do not misinterpret the absence of a summary as content to classify</t>
+  </si>
+  <si>
+    <t>{"eval_name": "summarization_accuracy_check", "trace_id": "019c153c-23b4-7d51-ba28-3a3cb72a2e02", "critique": {"eval_correct": true, "error_type": "none", "justification": "The evaluator followed the prompt: it used only the provided inputs, recognized that summary_output was null, and produced the mandated JSON object with the required fields 'items' and 'overall_reason'. It did not fabricate claims or introduce new criteria. The reasoning that no span-level alignment can be performed without a summary is accurate and aligns with the verdict. The presence of 'overall_score' is acceptable per the clarification about externally injected metadata and does not affect compliance.", "few_shot_example": null, "do's": "Adhere to the output_structure_mandate with 'items' and 'overall_reason', Base conclusions strictly on the provided context_span and summary_output, Explain in 'overall_reason' when comparison cannot be performed due to missing summary, Avoid introducing unauthorized criteria or extra commentary outside mandated fields", "don't's": "Do not fabricate comparisons when summary_output is null, Do not contradict the inputs, Do not add free-form commentary outside the mandated JSON fields, Do not misinterpret the absence of a summary as content to classify"}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -998,19 +1125,6 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1026,7 +1140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1049,20 +1163,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1077,12 +1182,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1527,7 +1626,7 @@
     </row>
     <row r="10" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>235</v>
+        <v>151</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -1703,7 +1802,7 @@
         <v>41</v>
       </c>
       <c r="U1" t="s">
-        <v>235</v>
+        <v>151</v>
       </c>
       <c r="V1" t="s">
         <v>42</v>
@@ -2985,1055 +3084,657 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811F2431-7BC9-4AF7-9FAA-32A7B52811FC}">
-  <dimension ref="A1:H67"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0840438-698F-4439-8E82-0401674533F6}">
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="40.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.90625" customWidth="1"/>
-    <col min="8" max="8" width="251.08984375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" t="s">
         <v>145</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" t="s">
         <v>146</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" t="s">
         <v>147</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J1" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="K1" t="s">
         <v>149</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="L1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="9" t="s">
+      <c r="E2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K2" t="s">
+        <v>160</v>
+      </c>
+      <c r="L2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="9" t="b">
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F3" t="b">
         <v>0</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.86</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="G3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.93</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="B4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" t="s">
+        <v>150</v>
+      </c>
+      <c r="I4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K4" t="s">
+        <v>170</v>
+      </c>
+      <c r="L4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="7" t="b">
+      <c r="B5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" t="b">
         <v>0</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.93</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J5" t="s">
+        <v>177</v>
+      </c>
+      <c r="K5" t="s">
+        <v>178</v>
+      </c>
+      <c r="L5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="7" t="b">
+      <c r="B6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" t="b">
         <v>0</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.86</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="G6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J6" t="s">
+        <v>182</v>
+      </c>
+      <c r="K6" t="s">
+        <v>183</v>
+      </c>
+      <c r="L6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.98</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="B7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
         <v>173</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="E7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H7" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7" t="s">
+        <v>188</v>
+      </c>
+      <c r="K7" t="s">
+        <v>189</v>
+      </c>
+      <c r="L7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="8" t="b">
+      <c r="B8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.86</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="8" t="s">
+      <c r="G8" t="s">
+        <v>150</v>
+      </c>
+      <c r="H8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I8" t="s">
+        <v>150</v>
+      </c>
+      <c r="J8" t="s">
+        <v>193</v>
+      </c>
+      <c r="K8" t="s">
+        <v>194</v>
+      </c>
+      <c r="L8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="8" t="b">
+      <c r="B9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="D9" t="s">
         <v>197</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="E9" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="7" t="s">
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J9" t="s">
+        <v>201</v>
+      </c>
+      <c r="K9" t="s">
+        <v>202</v>
+      </c>
+      <c r="L9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="7" t="b">
+      <c r="B10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" t="b">
         <v>0</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="G10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I10" t="s">
+        <v>150</v>
+      </c>
+      <c r="J10" t="s">
+        <v>206</v>
+      </c>
+      <c r="K10" t="s">
+        <v>207</v>
+      </c>
+      <c r="L10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E11" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>212</v>
+      </c>
+      <c r="H11" t="s">
+        <v>213</v>
+      </c>
+      <c r="I11" t="s">
+        <v>210</v>
+      </c>
+      <c r="J11" t="s">
+        <v>214</v>
+      </c>
+      <c r="K11" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>219</v>
+      </c>
+      <c r="H12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I12" t="s">
+        <v>210</v>
+      </c>
+      <c r="J12" t="s">
+        <v>221</v>
+      </c>
+      <c r="K12" t="s">
+        <v>222</v>
+      </c>
+      <c r="L12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" t="s">
+        <v>224</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" t="s">
+        <v>150</v>
+      </c>
+      <c r="I13" t="s">
+        <v>150</v>
+      </c>
+      <c r="J13" t="s">
+        <v>225</v>
+      </c>
+      <c r="K13" t="s">
+        <v>226</v>
+      </c>
+      <c r="L13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>230</v>
+      </c>
+      <c r="H14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I14" t="s">
+        <v>173</v>
+      </c>
+      <c r="J14" t="s">
+        <v>232</v>
+      </c>
+      <c r="K14" t="s">
+        <v>233</v>
+      </c>
+      <c r="L14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" t="s">
         <v>235</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H15" t="s">
+        <v>238</v>
+      </c>
+      <c r="I15" t="s">
+        <v>173</v>
+      </c>
+      <c r="J15" t="s">
+        <v>239</v>
+      </c>
+      <c r="K15" t="s">
+        <v>240</v>
+      </c>
+      <c r="L15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>123</v>
       </c>
-      <c r="C40" s="8" t="b">
+      <c r="B16" t="s">
+        <v>228</v>
+      </c>
+      <c r="C16" t="b">
         <v>0</v>
       </c>
-      <c r="D40" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B53" s="7" t="s">
+      <c r="D16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" t="s">
+        <v>242</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>243</v>
+      </c>
+      <c r="H16" t="s">
+        <v>244</v>
+      </c>
+      <c r="I16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J16" t="s">
+        <v>245</v>
+      </c>
+      <c r="K16" t="s">
+        <v>246</v>
+      </c>
+      <c r="L16" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>123</v>
       </c>
-      <c r="C53" s="7" t="b">
+      <c r="B17" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C54" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0.86</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E66" s="7">
-        <v>0.92</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.86</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>234</v>
+      <c r="G17" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" t="s">
+        <v>150</v>
+      </c>
+      <c r="J17" t="s">
+        <v>250</v>
+      </c>
+      <c r="K17" t="s">
+        <v>251</v>
+      </c>
+      <c r="L17" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H10:H14"/>
-    <mergeCell ref="A15:A27"/>
-    <mergeCell ref="B15:B27"/>
-    <mergeCell ref="C15:C27"/>
-    <mergeCell ref="D15:D27"/>
-    <mergeCell ref="E15:E27"/>
-    <mergeCell ref="G15:G27"/>
-    <mergeCell ref="H15:H27"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="C10:C14"/>
-    <mergeCell ref="D10:D14"/>
-    <mergeCell ref="E10:E14"/>
-    <mergeCell ref="G10:G14"/>
-    <mergeCell ref="H28:H38"/>
-    <mergeCell ref="A40:A52"/>
-    <mergeCell ref="B40:B52"/>
-    <mergeCell ref="C40:C52"/>
-    <mergeCell ref="D40:D52"/>
-    <mergeCell ref="E40:E52"/>
-    <mergeCell ref="G40:G52"/>
-    <mergeCell ref="H40:H52"/>
-    <mergeCell ref="A28:A38"/>
-    <mergeCell ref="B28:B38"/>
-    <mergeCell ref="C28:C38"/>
-    <mergeCell ref="D28:D38"/>
-    <mergeCell ref="E28:E38"/>
-    <mergeCell ref="G28:G38"/>
-    <mergeCell ref="H54:H64"/>
-    <mergeCell ref="A54:A64"/>
-    <mergeCell ref="B54:B64"/>
-    <mergeCell ref="C54:C64"/>
-    <mergeCell ref="D54:D64"/>
-    <mergeCell ref="E54:E64"/>
-    <mergeCell ref="G54:G64"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>